--- a/tests/branch_structures_mouse.xlsx
+++ b/tests/branch_structures_mouse.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\doctor\wyq\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\doctor\StrucGAP\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F22CBCF-4401-4A1D-AB24-0033D2B39F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87326B4-E419-433D-9261-7355BBD404DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4500" yWindow="3045" windowWidth="21600" windowHeight="12630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="69">
   <si>
     <t>Numbering</t>
   </si>
@@ -224,6 +224,10 @@
   </si>
   <si>
     <t>E2F1G4gfF3fe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E1e</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -543,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" customWidth="1"/>
@@ -870,6 +874,14 @@
         <v>67</v>
       </c>
     </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
